--- a/data/trans_bre/IP16A02-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP16A02-Provincia-trans_bre.xlsx
@@ -602,7 +602,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -660,49 +660,49 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-55,42; 9,55</t>
+          <t>-54,73; 7,93</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-31,36; 19,55</t>
+          <t>-30,9; 18,3</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-21,71; 24,07</t>
+          <t>-23,57; 25,31</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-31,43; 15,23</t>
+          <t>-28,03; 15,6</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-81,95; 34,47</t>
+          <t>-83,54; 28,22</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-60,27; 66,28</t>
+          <t>-60,56; 63,3</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-47,03; 86,13</t>
+          <t>-48,75; 101,66</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-77,62; 107,62</t>
+          <t>-75,26; 119,09</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -760,49 +760,49 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-27,48; 14,23</t>
+          <t>-26,11; 13,86</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-24,78; 14,04</t>
+          <t>-21,51; 14,75</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-35,0; 8,03</t>
+          <t>-33,01; 8,7</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-57,13; 16,54</t>
+          <t>-54,73; 15,48</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-80,45; 106,42</t>
+          <t>-75,53; 116,08</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-42,64; 39,66</t>
+          <t>-38,13; 42,24</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-59,24; 24,16</t>
+          <t>-57,43; 25,16</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-82,06; 29,22</t>
+          <t>-82,0; 26,47</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-53,01; 8,49</t>
+          <t>-47,35; 13,13</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,6; 40,24</t>
+          <t>-6,66; 39,51</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-34,36; 38,56</t>
+          <t>-33,4; 37,8</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 41,79</t>
+          <t>1,08; 41,69</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-88,98; 53,97</t>
+          <t>-87,87; 107,34</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-15,68; 156,66</t>
+          <t>-13,19; 140,28</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-66,16; 338,57</t>
+          <t>-67,95; 376,5</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-15,51; 984,23</t>
+          <t>-18,77; 929,05</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-27,04; 29,96</t>
+          <t>-28,63; 28,19</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-21,59; 29,21</t>
+          <t>-22,78; 27,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-8,86; 30,3</t>
+          <t>-12,22; 29,19</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-49,93; 21,14</t>
+          <t>-51,81; 19,06</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-50,69; 119,59</t>
+          <t>-52,6; 102,84</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-47,08; 163,13</t>
+          <t>-49,09; 143,97</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-20,08; 129,6</t>
+          <t>-26,21; 129,31</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-64,54; 48,07</t>
+          <t>-64,05; 40,04</t>
         </is>
       </c>
     </row>
@@ -1060,49 +1060,49 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-53,58; 12,72</t>
+          <t>-53,7; 12,17</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-14,25; 48,88</t>
+          <t>-10,93; 45,1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-40,1; 39,6</t>
+          <t>-47,13; 35,89</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-20,79; 52,01</t>
+          <t>-24,28; 50,92</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 169,61</t>
+          <t>-100,0; 242,33</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-22,29; 216,03</t>
+          <t>-16,72; 188,32</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-77,92; 369,76</t>
+          <t>-83,88; 317,19</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-35,4; 263,36</t>
+          <t>-39,11; 295,45</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1160,32 +1160,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-37,0; 31,61</t>
+          <t>-36,95; 32,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-34,0; 23,24</t>
+          <t>-33,12; 23,11</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-19,7; 27,13</t>
+          <t>-23,19; 27,12</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-41,12; 21,07</t>
+          <t>-44,91; 20,36</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-65,43; 136,32</t>
+          <t>-66,46; 134,18</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-67,45; 86,1</t>
+          <t>-69,31; 81,42</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1195,14 +1195,14 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-82,78; 91,48</t>
+          <t>-93,8; 81,78</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-13,05; 32,54</t>
+          <t>-14,22; 35,57</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,36; 33,87</t>
+          <t>-3,18; 36,55</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-24,15; 32,86</t>
+          <t>-26,43; 29,98</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,69; 36,23</t>
+          <t>-5,01; 36,57</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-25,88; 113,96</t>
+          <t>-27,35; 144,81</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-16,48; 211,96</t>
+          <t>-13,66; 243,56</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-37,7; 113,59</t>
+          <t>-41,48; 103,64</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-11,46; 120,68</t>
+          <t>-9,31; 112,67</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-30,77; 6,29</t>
+          <t>-30,51; 7,69</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-32,71; 9,07</t>
+          <t>-33,44; 10,45</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-14,31; 23,82</t>
+          <t>-14,9; 23,69</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-45,3; 26,84</t>
+          <t>-47,39; 24,71</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-56,6; 17,48</t>
+          <t>-55,96; 20,37</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-67,26; 40,43</t>
+          <t>-68,28; 43,11</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-32,72; 95,57</t>
+          <t>-34,5; 95,06</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-69,7; 69,51</t>
+          <t>-70,05; 68,88</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-18,03; 1,06</t>
+          <t>-18,63; 0,56</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-5,29; 11,5</t>
+          <t>-5,55; 11,33</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-6,67; 11,02</t>
+          <t>-7,22; 11,68</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-22,03; 7,81</t>
+          <t>-21,18; 8,71</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-38,72; 3,0</t>
+          <t>-40,44; 1,45</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-12,09; 33,54</t>
+          <t>-13,26; 32,22</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-16,06; 34,85</t>
+          <t>-17,78; 36,04</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-43,99; 18,62</t>
+          <t>-44,96; 21,0</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16A02-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP16A02-Provincia-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-54,73; 7,93</t>
+          <t>-52,54; 9,44</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-30,9; 18,3</t>
+          <t>-28,09; 19,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-23,57; 25,31</t>
+          <t>-24,05; 24,28</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-28,03; 15,6</t>
+          <t>-31,48; 17,08</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-83,54; 28,22</t>
+          <t>-84,7; 32,53</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-60,56; 63,3</t>
+          <t>-56,09; 60,54</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-48,75; 101,66</t>
+          <t>-50,64; 96,55</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-75,26; 119,09</t>
+          <t>-75,44; 129,91</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-26,11; 13,86</t>
+          <t>-27,09; 13,58</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-21,51; 14,75</t>
+          <t>-20,9; 16,97</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-33,01; 8,7</t>
+          <t>-33,52; 10,74</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-54,73; 15,48</t>
+          <t>-52,98; 16,07</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-75,53; 116,08</t>
+          <t>-80,48; 100,81</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-38,13; 42,24</t>
+          <t>-39,35; 47,87</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-57,43; 25,16</t>
+          <t>-58,35; 37,82</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-82,0; 26,47</t>
+          <t>-76,86; 27,82</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-47,35; 13,13</t>
+          <t>-49,81; 8,56</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,66; 39,51</t>
+          <t>-9,93; 40,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-33,4; 37,8</t>
+          <t>-33,57; 38,3</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,08; 41,69</t>
+          <t>-0,5; 41,67</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-87,87; 107,34</t>
+          <t>-90,08; 51,48</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-13,19; 140,28</t>
+          <t>-19,52; 140,51</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-67,95; 376,5</t>
+          <t>-70,74; 278,71</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-18,77; 929,05</t>
+          <t>-17,87; 960,18</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-28,63; 28,19</t>
+          <t>-28,6; 28,78</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-22,78; 27,0</t>
+          <t>-22,62; 26,3</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-12,22; 29,19</t>
+          <t>-11,54; 29,87</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-51,81; 19,06</t>
+          <t>-51,82; 19,34</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-52,6; 102,84</t>
+          <t>-51,36; 111,13</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-49,09; 143,97</t>
+          <t>-49,49; 138,54</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-26,21; 129,31</t>
+          <t>-25,01; 131,1</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-64,05; 40,04</t>
+          <t>-66,64; 39,31</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-53,7; 12,17</t>
+          <t>-56,84; 13,12</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-10,93; 45,1</t>
+          <t>-11,63; 45,29</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-47,13; 35,89</t>
+          <t>-40,61; 37,86</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-24,28; 50,92</t>
+          <t>-19,29; 51,86</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 242,33</t>
+          <t>-100,0; 215,72</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-16,72; 188,32</t>
+          <t>-17,89; 199,29</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-83,88; 317,19</t>
+          <t>-78,77; 383,61</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-39,11; 295,45</t>
+          <t>-36,89; 247,62</t>
         </is>
       </c>
     </row>
@@ -1160,32 +1160,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-36,95; 32,0</t>
+          <t>-36,58; 30,23</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-33,12; 23,11</t>
+          <t>-34,07; 24,03</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-23,19; 27,12</t>
+          <t>-20,04; 27,38</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-44,91; 20,36</t>
+          <t>-40,63; 24,65</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-66,46; 134,18</t>
+          <t>-62,21; 117,64</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-69,31; 81,42</t>
+          <t>-66,58; 105,27</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-93,8; 81,78</t>
+          <t>-84,04; 105,45</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-14,22; 35,57</t>
+          <t>-13,6; 33,87</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 36,55</t>
+          <t>-4,29; 33,41</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-26,43; 29,98</t>
+          <t>-23,66; 30,11</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,01; 36,57</t>
+          <t>-5,79; 36,32</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-27,35; 144,81</t>
+          <t>-27,34; 124,77</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-13,66; 243,56</t>
+          <t>-13,8; 211,31</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-41,48; 103,64</t>
+          <t>-39,26; 99,01</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-9,31; 112,67</t>
+          <t>-11,43; 112,97</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-30,51; 7,69</t>
+          <t>-30,29; 8,9</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-33,44; 10,45</t>
+          <t>-33,0; 8,65</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-14,9; 23,69</t>
+          <t>-15,86; 23,72</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-47,39; 24,71</t>
+          <t>-47,06; 21,14</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-55,96; 20,37</t>
+          <t>-56,08; 22,71</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-68,28; 43,11</t>
+          <t>-68,67; 32,16</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-34,5; 95,06</t>
+          <t>-34,93; 92,98</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-70,05; 68,88</t>
+          <t>-69,5; 62,51</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-18,63; 0,56</t>
+          <t>-17,37; 1,13</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-5,55; 11,33</t>
+          <t>-5,23; 12,13</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-7,22; 11,68</t>
+          <t>-6,86; 11,7</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-21,18; 8,71</t>
+          <t>-23,15; 7,93</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-40,44; 1,45</t>
+          <t>-38,08; 3,03</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-13,26; 32,22</t>
+          <t>-12,14; 33,94</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-17,78; 36,04</t>
+          <t>-16,31; 37,0</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-44,96; 21,0</t>
+          <t>-47,8; 18,84</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16A02-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP16A02-Provincia-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos para  el dolor y/o para bajar la fiebre</t>
+          <t>Menores que consumieron medicamentos para  el dolor y/o para bajar la fiebre</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-6,01</t>
+          <t>2,47</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-21,83%</t>
+          <t>9,91%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-52,54; 9,44</t>
+          <t>-55,42; 9,55</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-28,09; 19,02</t>
+          <t>-31,36; 19,55</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-24,05; 24,28</t>
+          <t>-21,71; 24,07</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-31,48; 17,08</t>
+          <t>-22,45; 23,52</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-84,7; 32,53</t>
+          <t>-81,95; 34,47</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-56,09; 60,54</t>
+          <t>-60,27; 66,28</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-50,64; 96,55</t>
+          <t>-47,03; 86,13</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-75,44; 129,91</t>
+          <t>-63,46; 192,14</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-19,77</t>
+          <t>4,96</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-32,98%</t>
+          <t>8,36%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-27,09; 13,58</t>
+          <t>-27,48; 14,23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-20,9; 16,97</t>
+          <t>-24,78; 14,04</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-33,52; 10,74</t>
+          <t>-35,0; 8,03</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-52,98; 16,07</t>
+          <t>-14,52; 23,8</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-80,48; 100,81</t>
+          <t>-80,45; 106,42</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-39,35; 47,87</t>
+          <t>-42,64; 39,66</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-58,35; 37,82</t>
+          <t>-59,24; 24,16</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-76,86; 27,82</t>
+          <t>-21,28; 48,17</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>20,91</t>
+          <t>21,22</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>173,75%</t>
+          <t>175,28%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-49,81; 8,56</t>
+          <t>-53,01; 8,49</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,93; 40,15</t>
+          <t>-8,6; 40,24</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-33,57; 38,3</t>
+          <t>-34,36; 38,56</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 41,67</t>
+          <t>0,25; 41,85</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-90,08; 51,48</t>
+          <t>-88,98; 53,97</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-19,52; 140,51</t>
+          <t>-15,68; 156,66</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-70,74; 278,71</t>
+          <t>-66,16; 338,57</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-17,87; 960,18</t>
+          <t>-17,12; 925,23</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-17,46</t>
+          <t>-21,98</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-25,6%</t>
+          <t>-31,29%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-28,6; 28,78</t>
+          <t>-27,04; 29,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-22,62; 26,3</t>
+          <t>-21,59; 29,21</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-11,54; 29,87</t>
+          <t>-8,86; 30,3</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-51,82; 19,34</t>
+          <t>-54,86; 14,54</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-51,36; 111,13</t>
+          <t>-50,69; 119,59</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-49,49; 138,54</t>
+          <t>-47,08; 163,13</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-25,01; 131,1</t>
+          <t>-20,08; 129,6</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-66,64; 39,31</t>
+          <t>-67,16; 33,67</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14,66</t>
+          <t>9,6</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>37,26%</t>
+          <t>21,45%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-56,84; 13,12</t>
+          <t>-53,58; 12,72</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-11,63; 45,29</t>
+          <t>-14,25; 48,88</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-40,61; 37,86</t>
+          <t>-40,1; 39,6</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-19,29; 51,86</t>
+          <t>-27,31; 47,92</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 215,72</t>
+          <t>-100,0; 169,61</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-17,89; 199,29</t>
+          <t>-22,29; 216,03</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-78,77; 383,61</t>
+          <t>-77,92; 369,76</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-36,89; 247,62</t>
+          <t>-42,48; 201,81</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-12,94</t>
+          <t>-12,02</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-33,54%</t>
+          <t>-31,41%</t>
         </is>
       </c>
     </row>
@@ -1160,32 +1160,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-36,58; 30,23</t>
+          <t>-37,0; 31,61</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-34,07; 24,03</t>
+          <t>-34,0; 23,24</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-20,04; 27,38</t>
+          <t>-19,7; 27,13</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-40,63; 24,65</t>
+          <t>-42,02; 21,54</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-62,21; 117,64</t>
+          <t>-65,43; 136,32</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-66,58; 105,27</t>
+          <t>-67,45; 86,1</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-84,04; 105,45</t>
+          <t>-82,04; 90,17</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15,38</t>
+          <t>15,25</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>35,09%</t>
+          <t>35,37%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-13,6; 33,87</t>
+          <t>-13,05; 32,54</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 33,41</t>
+          <t>-4,36; 33,87</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-23,66; 30,11</t>
+          <t>-24,15; 32,86</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,79; 36,32</t>
+          <t>-7,52; 35,92</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-27,34; 124,77</t>
+          <t>-25,88; 113,96</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-13,8; 211,31</t>
+          <t>-16,48; 211,96</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-39,26; 99,01</t>
+          <t>-37,7; 113,59</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-11,43; 112,97</t>
+          <t>-12,38; 122,62</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-11,82</t>
+          <t>-11,26</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>-22,33%</t>
+          <t>-21,59%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-30,29; 8,9</t>
+          <t>-30,77; 6,29</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-33,0; 8,65</t>
+          <t>-32,71; 9,07</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-15,86; 23,72</t>
+          <t>-14,31; 23,82</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-47,06; 21,14</t>
+          <t>-45,65; 30,58</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-56,08; 22,71</t>
+          <t>-56,6; 17,48</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-68,67; 32,16</t>
+          <t>-67,26; 40,43</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-34,93; 92,98</t>
+          <t>-32,72; 95,57</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-69,5; 62,51</t>
+          <t>-68,5; 81,55</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-3,72</t>
+          <t>4,73</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>-8,46%</t>
+          <t>10,75%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-17,37; 1,13</t>
+          <t>-18,03; 1,06</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-5,23; 12,13</t>
+          <t>-5,29; 11,5</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-6,86; 11,7</t>
+          <t>-6,67; 11,02</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-23,15; 7,93</t>
+          <t>-4,44; 14,82</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-38,08; 3,03</t>
+          <t>-38,72; 3,0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-12,14; 33,94</t>
+          <t>-12,09; 33,54</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-16,31; 37,0</t>
+          <t>-16,06; 34,85</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-47,8; 18,84</t>
+          <t>-8,95; 37,57</t>
         </is>
       </c>
     </row>
